--- a/owlcms/src/main/resources/templates/records/display_groups.xlsx
+++ b/owlcms/src/main/resources/templates/records/display_groups.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29029"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Dev\git\owlcms_v23\owlcms\src\main\resources\templates\records\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Dev\git\owlcms4\owlcms\src\main\resources\templates\records\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C440CB20-3C0F-4E34-92FB-10556CD9674E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="9690" windowWidth="29040" windowHeight="17520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Records" sheetId="1" r:id="rId1"/>
